--- a/data/trans_orig/P34A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>70548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108839</t>
+          <t>106518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55373</t>
+          <t>55476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>82559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133986</t>
+          <t>134840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178946</t>
+          <t>180686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87535</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>53635</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42424</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67290</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>124323</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>105144</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>146057</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40881</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68782</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>15,37%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>124323</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>103376</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>145030</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186454</t>
+          <t>185199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232093</t>
+          <t>230377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>202918</t>
+          <t>205232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239078</t>
+          <t>239891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>403864</t>
+          <t>403307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>460205</t>
+          <t>458575</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>71188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103664</t>
+          <t>105149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40988</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63581</t>
+          <t>63651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>119487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158305</t>
+          <t>161622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67696</t>
+          <t>66435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>41912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66292</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83870</t>
+          <t>85428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121486</t>
+          <t>120644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>53179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88502</t>
+          <t>89421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>34448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58157</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96386</t>
+          <t>95674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139701</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48544</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82117</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>74097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110927</t>
+          <t>112743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183225</t>
+          <t>180125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227552</t>
+          <t>225465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168780</t>
+          <t>168867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201293</t>
+          <t>200592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>362388</t>
+          <t>360934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>415461</t>
+          <t>416298</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64121</t>
+          <t>63486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97339</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71748</t>
+          <t>70994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119428</t>
+          <t>119107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158413</t>
+          <t>157758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>49397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>55458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80839</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87555</t>
+          <t>88187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124015</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79052</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86835</t>
+          <t>87259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76152</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>277328</t>
+          <t>278013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>570994</t>
+          <t>570112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65881</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87385</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357021</t>
+          <t>357227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>695347</t>
+          <t>714300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131359</t>
+          <t>131464</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33250</t>
+          <t>33595</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50839</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>49302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179090</t>
+          <t>176269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133476</t>
+          <t>137481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35248</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158517</t>
+          <t>157897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61231</t>
+          <t>59760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104640</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74932</t>
+          <t>75667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93941</t>
+          <t>89095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167873</t>
+          <t>163062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86590</t>
+          <t>87651</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137618</t>
+          <t>137629</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74160</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114983</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200430</t>
+          <t>200055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410651</t>
+          <t>412195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>484540</t>
+          <t>481226</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>446844</t>
+          <t>443732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>755626</t>
+          <t>761005</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>880439</t>
+          <t>879029</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1335023</t>
+          <t>1346587</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>189265</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244323</t>
+          <t>244310</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79281</t>
+          <t>71374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180141</t>
+          <t>181635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>241640</t>
+          <t>235734</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>409386</t>
+          <t>407744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153034</t>
+          <t>151338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206663</t>
+          <t>205702</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87813</t>
+          <t>83152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220507</t>
+          <t>221765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232821</t>
+          <t>238177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400580</t>
+          <t>401546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59320</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82235</t>
+          <t>85432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>43044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77306</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58745</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102201</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>151485</t>
+          <t>150537</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>194441</t>
+          <t>192655</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>362074</t>
+          <t>363045</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>522294</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>531001</t>
+          <t>536522</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>705891</t>
+          <t>722010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>91174</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>129564</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>176042</t>
+          <t>179918</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>299551</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>287281</t>
+          <t>288178</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>418344</t>
+          <t>411553</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>77651</t>
+          <t>78874</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>114471</t>
+          <t>114407</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>110529</t>
+          <t>114361</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>172473</t>
+          <t>176438</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>201222</t>
+          <t>200799</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>274883</t>
+          <t>277894</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45259</t>
+          <t>46525</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>89575</t>
+          <t>91700</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>77142</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>130854</t>
+          <t>130229</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>46271</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>90966</t>
+          <t>90147</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>31927</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58688</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84076</t>
+          <t>84088</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>141342</t>
+          <t>139803</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54697</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>104376</t>
+          <t>106271</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>279571</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>329992</t>
+          <t>330669</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>347714</t>
+          <t>350965</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>418475</t>
+          <t>422136</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>51413</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>199467</t>
+          <t>197707</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>245364</t>
+          <t>243158</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>213198</t>
+          <t>216438</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>272826</t>
+          <t>274025</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>132431</t>
+          <t>132722</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>177758</t>
+          <t>178756</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>139147</t>
+          <t>139854</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>188800</t>
+          <t>189918</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>303409</t>
+          <t>305329</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>443078</t>
+          <t>443180</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>189285</t>
+          <t>187211</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>266169</t>
+          <t>263272</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>527976</t>
+          <t>535824</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>689511</t>
+          <t>689169</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>311926</t>
+          <t>310041</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>461182</t>
+          <t>465622</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>171218</t>
+          <t>172270</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>244977</t>
+          <t>246671</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>521562</t>
+          <t>539322</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>687098</t>
+          <t>684178</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1370758</t>
+          <t>1362204</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1947861</t>
+          <t>2005315</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1618849</t>
+          <t>1614664</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2087070</t>
+          <t>2094314</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3053003</t>
+          <t>3041883</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3826876</t>
+          <t>3695326</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>461122</t>
+          <t>463200</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>658891</t>
+          <t>658290</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>616814</t>
+          <t>609571</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>825426</t>
+          <t>834658</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1156995</t>
+          <t>1178196</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1447888</t>
+          <t>1452496</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>345116</t>
+          <t>349804</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>506034</t>
+          <t>509879</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>505556</t>
+          <t>501247</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>680465</t>
+          <t>678382</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>926228</t>
+          <t>942739</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1162066</t>
+          <t>1157528</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88155</t>
+          <t>93878</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>77173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106518</t>
+          <t>114764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67506</t>
+          <t>75009</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>93391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>155661</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134840</t>
+          <t>145211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180686</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70687</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>60945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>95489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>56041</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>43533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67290</t>
+          <t>72821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124323</t>
+          <t>132087</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105144</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146057</t>
+          <t>155833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>207651</t>
+          <t>230901</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>185199</t>
+          <t>207486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230377</t>
+          <t>255708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>222519</t>
+          <t>242946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205232</t>
+          <t>224308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239891</t>
+          <t>263041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>430169</t>
+          <t>473847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>403307</t>
+          <t>444794</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458575</t>
+          <t>504730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86641</t>
+          <t>92990</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71188</t>
+          <t>75795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105149</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51427</t>
+          <t>57271</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>45968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>69338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>138068</t>
+          <t>150261</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119487</t>
+          <t>128745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161622</t>
+          <t>174358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>54250</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>40562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66435</t>
+          <t>72080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>57143</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>71170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>101913</t>
+          <t>111393</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>91990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120644</t>
+          <t>134350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>548065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>950134</t>
+          <t>1036476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70023</t>
+          <t>71759</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89421</t>
+          <t>89523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>59200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114708</t>
+          <t>118777</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>99224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138709</t>
+          <t>140405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>90260</t>
+          <t>97665</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>80805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112743</t>
+          <t>120039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203735</t>
+          <t>221407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180125</t>
+          <t>198254</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225465</t>
+          <t>243536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184950</t>
+          <t>205629</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168867</t>
+          <t>187863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200592</t>
+          <t>223652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>388685</t>
+          <t>427036</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>360934</t>
+          <t>399574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>416298</t>
+          <t>455051</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>67940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99093</t>
+          <t>101868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>62977</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47907</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70994</t>
+          <t>75512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>137472</t>
+          <t>147404</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119107</t>
+          <t>129069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157758</t>
+          <t>169446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>39094</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49397</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>67536</t>
+          <t>76379</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55458</t>
+          <t>63360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>90553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>103668</t>
+          <t>115473</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88187</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119886</t>
+          <t>133017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80531</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>56257</t>
+          <t>63991</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87259</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>39048</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>52083</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>67698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>426702</t>
+          <t>204284</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>278013</t>
+          <t>182858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>570112</t>
+          <t>225896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76266</t>
+          <t>84716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65968</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>96487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>502967</t>
+          <t>288999</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357227</t>
+          <t>261687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>714300</t>
+          <t>312314</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78188</t>
+          <t>86299</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>69283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131464</t>
+          <t>104448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,22 +2463,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>47029</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>119500</t>
+          <t>133329</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49302</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176269</t>
+          <t>151933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>80494</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137481</t>
+          <t>107257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>106800</t>
+          <t>119026</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>100071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157897</t>
+          <t>136944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>667274</t>
+          <t>470667</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166749</t>
+          <t>186761</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>834022</t>
+          <t>657428</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>87170</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59760</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104771</t>
+          <t>111944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>56807</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27576</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75667</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>134195</t>
+          <t>143976</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>117423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163062</t>
+          <t>171327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>109898</t>
+          <t>117411</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87651</t>
+          <t>93798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137629</t>
+          <t>144778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>56696</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>44400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>71954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>163313</t>
+          <t>174108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116593</t>
+          <t>143408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200055</t>
+          <t>206593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>445947</t>
+          <t>495143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>412195</t>
+          <t>454930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>481226</t>
+          <t>526677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>562954</t>
+          <t>398347</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>443732</t>
+          <t>373172</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>761005</t>
+          <t>423585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1008901</t>
+          <t>893491</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>879029</t>
+          <t>848094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1346587</t>
+          <t>937657</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>216662</t>
+          <t>232587</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>206353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244310</t>
+          <t>260433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>137612</t>
+          <t>160241</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71374</t>
+          <t>140573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181635</t>
+          <t>180945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>354274</t>
+          <t>392829</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>235734</t>
+          <t>360652</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>407744</t>
+          <t>428638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>178757</t>
+          <t>195377</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151338</t>
+          <t>169947</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>205702</t>
+          <t>222828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>169251</t>
+          <t>188017</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>165730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221765</t>
+          <t>209999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>348008</t>
+          <t>383394</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>238177</t>
+          <t>353021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401546</t>
+          <t>418210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1031136</t>
+          <t>1127688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>977556</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2008692</t>
+          <t>1987798</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>57041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85432</t>
+          <t>84686</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>73639</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>97393</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102132</t>
+          <t>124010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>171432</t>
+          <t>200633</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>150537</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>192655</t>
+          <t>225966</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>417738</t>
+          <t>402711</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>363045</t>
+          <t>379673</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>519194</t>
+          <t>427799</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>589170</t>
+          <t>603343</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>536522</t>
+          <t>567340</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>722010</t>
+          <t>636701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>121392</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>102382</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>129564</t>
+          <t>143963</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>228787</t>
+          <t>214835</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>179918</t>
+          <t>194379</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>237459</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>338096</t>
+          <t>336226</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>288178</t>
+          <t>308903</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>411553</t>
+          <t>364916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>94416</t>
+          <t>128581</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>114407</t>
+          <t>153452</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>149912</t>
+          <t>163879</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>114361</t>
+          <t>144698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>176438</t>
+          <t>185227</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>244327</t>
+          <t>292460</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>200799</t>
+          <t>266474</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>277894</t>
+          <t>324027</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>472993</t>
+          <t>565648</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>837069</t>
+          <t>828073</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1310061</t>
+          <t>1393721</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>67021</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>91700</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>35570</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>56530</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>100873</t>
+          <t>108078</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>78858</t>
+          <t>83327</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>130229</t>
+          <t>135680</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>65907</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>90147</t>
+          <t>87224</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>43797</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>63223</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>109704</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84088</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>139803</t>
+          <t>141088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>77113</t>
+          <t>77444</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>106271</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>305623</t>
+          <t>341553</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>279571</t>
+          <t>314914</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>330669</t>
+          <t>371737</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>382736</t>
+          <t>418998</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>350965</t>
+          <t>383852</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422136</t>
+          <t>452294</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51413</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>220557</t>
+          <t>245486</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>197707</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>243158</t>
+          <t>272482</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>242210</t>
+          <t>265220</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>234470</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>274025</t>
+          <t>297846</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>152987</t>
+          <t>165048</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>132722</t>
+          <t>141204</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>178756</t>
+          <t>188355</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>163518</t>
+          <t>174031</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>139854</t>
+          <t>150392</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>189918</t>
+          <t>197404</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>758535</t>
+          <t>840854</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>999042</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>389240</t>
+          <t>414100</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>305329</t>
+          <t>368462</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>443180</t>
+          <t>459334</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>231770</t>
+          <t>253909</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>187211</t>
+          <t>227721</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>263272</t>
+          <t>285885</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>621010</t>
+          <t>668008</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>535824</t>
+          <t>615128</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>689169</t>
+          <t>723906</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>403255</t>
+          <t>436717</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>310041</t>
+          <t>392975</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>465622</t>
+          <t>489444</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>211995</t>
+          <t>228374</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>172270</t>
+          <t>199759</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>246671</t>
+          <t>258420</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>615250</t>
+          <t>665091</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>539322</t>
+          <t>610537</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>684178</t>
+          <t>724152</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1532580</t>
+          <t>1429812</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1362204</t>
+          <t>1365327</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2005315</t>
+          <t>1492399</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1770049</t>
+          <t>1675903</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1614664</t>
+          <t>1617603</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2094314</t>
+          <t>1724857</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3302629</t>
+          <t>3105715</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3041883</t>
+          <t>3019979</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3695326</t>
+          <t>3186601</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>591851</t>
+          <t>637429</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>463200</t>
+          <t>593676</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>658290</t>
+          <t>689290</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>737769</t>
+          <t>787839</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>609571</t>
+          <t>743671</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>834658</t>
+          <t>835064</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1329620</t>
+          <t>1425268</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1178196</t>
+          <t>1365892</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1452496</t>
+          <t>1498621</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>449863</t>
+          <t>514450</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>349804</t>
+          <t>473144</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>509879</t>
+          <t>567344</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>618373</t>
+          <t>681327</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>501247</t>
+          <t>639237</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>678382</t>
+          <t>723178</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1068236</t>
+          <t>1195778</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>942739</t>
+          <t>1131937</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1157528</t>
+          <t>1260116</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3366789</t>
+          <t>3432508</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3569956</t>
+          <t>3627352</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6936745</t>
+          <t>7059860</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
